--- a/data/trans_orig/IP17-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP17-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20549</t>
+          <t>20722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35559</t>
+          <t>37243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24065</t>
+          <t>24861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39843</t>
+          <t>40810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48928</t>
+          <t>50487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71588</t>
+          <t>71968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103167</t>
+          <t>101483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118177</t>
+          <t>118004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113234</t>
+          <t>112267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129012</t>
+          <t>128216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220215</t>
+          <t>219835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242875</t>
+          <t>241316</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35857</t>
+          <t>35812</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54673</t>
+          <t>54666</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37820</t>
+          <t>38288</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57954</t>
+          <t>57803</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79444</t>
+          <t>79572</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105489</t>
+          <t>105490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140490</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159306</t>
+          <t>159351</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154188</t>
+          <t>154339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174322</t>
+          <t>173854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>301816</t>
+          <t>301815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327861</t>
+          <t>327733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31766</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26398</t>
+          <t>26779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42157</t>
+          <t>42419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46888</t>
+          <t>47217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68526</t>
+          <t>68305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106051</t>
+          <t>106838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120280</t>
+          <t>120466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107500</t>
+          <t>107238</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123259</t>
+          <t>122878</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>218948</t>
+          <t>219169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240586</t>
+          <t>240257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29240</t>
+          <t>28498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46984</t>
+          <t>47377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38938</t>
+          <t>38276</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58813</t>
+          <t>58264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71101</t>
+          <t>72869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98374</t>
+          <t>100459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162331</t>
+          <t>161938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180075</t>
+          <t>180817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149011</t>
+          <t>149560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>168886</t>
+          <t>169548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>318765</t>
+          <t>316680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346038</t>
+          <t>344270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116961</t>
+          <t>116903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149439</t>
+          <t>151293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143277</t>
+          <t>143533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179505</t>
+          <t>179665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>271234</t>
+          <t>272281</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317509</t>
+          <t>320747</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>531582</t>
+          <t>529728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>564060</t>
+          <t>564118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>543195</t>
+          <t>543035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>579423</t>
+          <t>579167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1086212</t>
+          <t>1082974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1132487</t>
+          <t>1131440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41501</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23869</t>
+          <t>24177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41232</t>
+          <t>41247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53437</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77152</t>
+          <t>77243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97856</t>
+          <t>97815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114304</t>
+          <t>114343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112451</t>
+          <t>112436</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129814</t>
+          <t>129506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>215888</t>
+          <t>215797</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239603</t>
+          <t>239605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37940</t>
+          <t>37195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56981</t>
+          <t>56948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>42253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63840</t>
+          <t>63865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85399</t>
+          <t>85891</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115033</t>
+          <t>113752</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148702</t>
+          <t>148735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167743</t>
+          <t>168488</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159322</t>
+          <t>159297</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179892</t>
+          <t>180909</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>313812</t>
+          <t>315093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>343446</t>
+          <t>342954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24904</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41058</t>
+          <t>41418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34366</t>
+          <t>33895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>51482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63127</t>
+          <t>64165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87726</t>
+          <t>89045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114318</t>
+          <t>113958</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130472</t>
+          <t>129877</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113764</t>
+          <t>114485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131601</t>
+          <t>132072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>233617</t>
+          <t>232298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>258216</t>
+          <t>257178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41296</t>
+          <t>40804</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61789</t>
+          <t>61186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>34045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53735</t>
+          <t>53199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>79729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109403</t>
+          <t>108893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147748</t>
+          <t>148351</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168241</t>
+          <t>168733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154661</t>
+          <t>155197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174340</t>
+          <t>174351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308530</t>
+          <t>309040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>339222</t>
+          <t>338204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145520</t>
+          <t>145285</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180809</t>
+          <t>183629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151924</t>
+          <t>151532</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189534</t>
+          <t>188742</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>307151</t>
+          <t>307721</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>360128</t>
+          <t>361743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>529144</t>
+          <t>526324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>564433</t>
+          <t>564668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>561675</t>
+          <t>562467</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>599285</t>
+          <t>599677</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1101034</t>
+          <t>1099419</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1154011</t>
+          <t>1153441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17060</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32638</t>
+          <t>32346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39605</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44119</t>
+          <t>43761</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66318</t>
+          <t>67242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100464</t>
+          <t>100756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116042</t>
+          <t>115904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108471</t>
+          <t>108090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125650</t>
+          <t>125805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>214860</t>
+          <t>213936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237059</t>
+          <t>237417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43185</t>
+          <t>42718</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62756</t>
+          <t>62252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39057</t>
+          <t>39432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59266</t>
+          <t>58469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87369</t>
+          <t>86856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114269</t>
+          <t>113733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143795</t>
+          <t>144299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163366</t>
+          <t>163833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164359</t>
+          <t>165156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184568</t>
+          <t>184193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>315907</t>
+          <t>316443</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>342807</t>
+          <t>343320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>23207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38282</t>
+          <t>38476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23365</t>
+          <t>22496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38882</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>50191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73098</t>
+          <t>71687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117715</t>
+          <t>117521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132380</t>
+          <t>132790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126619</t>
+          <t>126746</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142136</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248400</t>
+          <t>249811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271172</t>
+          <t>271307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47617</t>
+          <t>47320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28386</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46692</t>
+          <t>47045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61450</t>
+          <t>61592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88227</t>
+          <t>89140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159803</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179715</t>
+          <t>178711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156963</t>
+          <t>156610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175269</t>
+          <t>175226</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322848</t>
+          <t>321935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>349625</t>
+          <t>349483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,02%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>128350</t>
+          <t>127645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163278</t>
+          <t>161928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129406</t>
+          <t>129843</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164987</t>
+          <t>164378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264740</t>
+          <t>266751</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>313988</t>
+          <t>316631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>539792</t>
+          <t>541142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>574720</t>
+          <t>575425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>575870</t>
+          <t>576479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>611451</t>
+          <t>611014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1129939</t>
+          <t>1127296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1179187</t>
+          <t>1177176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24113</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>31408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29739</t>
+          <t>29566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50832</t>
+          <t>49343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93167</t>
+          <t>93781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105627</t>
+          <t>105634</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109973</t>
+          <t>109004</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126002</t>
+          <t>126036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>206861</t>
+          <t>208350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227954</t>
+          <t>228127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,53%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38732</t>
+          <t>38493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61939</t>
+          <t>61545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64697</t>
+          <t>65442</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92821</t>
+          <t>93257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151977</t>
+          <t>151897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168898</t>
+          <t>168936</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193096</t>
+          <t>193490</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216303</t>
+          <t>216542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>352727</t>
+          <t>352291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>380851</t>
+          <t>380106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39698</t>
+          <t>38079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22303</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42622</t>
+          <t>42353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42297</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73352</t>
+          <t>74836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149887</t>
+          <t>151506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173308</t>
+          <t>174391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142664</t>
+          <t>142933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162983</t>
+          <t>163237</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301519</t>
+          <t>300035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>332574</t>
+          <t>332304</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>21039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>36591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>20918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37658</t>
+          <t>38161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45733</t>
+          <t>45453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68057</t>
+          <t>68547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>131376</t>
+          <t>131371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147077</t>
+          <t>146923</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143580</t>
+          <t>143077</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160419</t>
+          <t>160320</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281144</t>
+          <t>280654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303468</t>
+          <t>303748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83926</t>
+          <t>82080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120598</t>
+          <t>116826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113277</t>
+          <t>113296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149728</t>
+          <t>151520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206386</t>
+          <t>207822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>259768</t>
+          <t>258123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544742</t>
+          <t>548514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>581414</t>
+          <t>583260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>612244</t>
+          <t>610452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>648695</t>
+          <t>648676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1167544</t>
+          <t>1169189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1220926</t>
+          <t>1219490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP17-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP17-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32127</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23989</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40929</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,74%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>28082</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>20722</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37243</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36568</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>20,24%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>14,94%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>32127</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24861</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>40810</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50487</t>
+          <t>50156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71968</t>
+          <t>72477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>120950</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>112148</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>129088</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>110644</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>101483</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>102158</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>118004</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>79,76%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>73,64%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>85,06%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>120950</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>112267</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>128216</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>73,34%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>342</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219835</t>
+          <t>219326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241316</t>
+          <t>241647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47746</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>38540</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>57765</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18,17%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>44763</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>35812</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54666</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>36066</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>54063</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>22,94%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>47746</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>38288</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>57803</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79572</t>
+          <t>79019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105490</t>
+          <t>105807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>164396</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>154377</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>173602</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>77,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>81,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>150400</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>140497</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>159351</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>141100</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>159097</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>77,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>164396</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>154339</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>173854</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>77,49%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>301815</t>
+          <t>301498</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327733</t>
+          <t>328286</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34003</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26336</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42369</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22,72%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>23496</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17351</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30979</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16663</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>30632</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>34003</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>26779</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>42419</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47217</t>
+          <t>48144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68305</t>
+          <t>68781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>115654</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>107288</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>123321</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>77,28%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>71,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>82,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>114321</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>106838</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>120466</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>107185</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>121154</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>82,95%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>115654</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>107238</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>122878</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>77,28%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219169</t>
+          <t>218693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240257</t>
+          <t>239330</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>47960</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38963</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>58140</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>37247</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28498</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>47377</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>27800</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>47256</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>47960</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38276</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>58264</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72869</t>
+          <t>72327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100459</t>
+          <t>100055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>159864</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149684</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>168861</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>172068</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>161938</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>180817</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>162059</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>181515</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>159864</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>149560</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>169548</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>76,92%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316680</t>
+          <t>317084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>344270</t>
+          <t>344812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>144249</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>180387</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>19,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>133587</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>116903</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>151293</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>118374</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>150599</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>19,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>161836</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>143533</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>179665</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272281</t>
+          <t>272305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320747</t>
+          <t>320612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>560864</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>542313</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>578451</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>77,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>80,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>817</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>547434</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>529728</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>564118</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>530422</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>562647</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>80,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>77,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>560864</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>543035</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>579167</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>77,61%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1082974</t>
+          <t>1083109</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1131440</t>
+          <t>1131416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2012 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32413</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24140</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41641</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32299</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25014</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41542</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24071</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40693</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23,18%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>32413</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24177</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>41247</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53435</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77243</t>
+          <t>77596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121270</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>112042</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>129543</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>78,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>107058</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>97815</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>114343</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>98664</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>115286</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>76,82%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,05%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121270</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>112436</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>129506</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>78,91%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>215797</t>
+          <t>215444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239605</t>
+          <t>240011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153683</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153683</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153683</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153683</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153683</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>52445</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43050</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>63349</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>46851</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>37195</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56948</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>37493</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>56014</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>22,78%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>52445</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>42253</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>63865</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>23,5%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85891</t>
+          <t>86042</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113752</t>
+          <t>114619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>170717</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>159813</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>180112</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>158832</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>148735</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>168488</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>149669</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>168190</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>77,22%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>170717</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>159297</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>180909</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>76,5%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>315093</t>
+          <t>314226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>342954</t>
+          <t>342803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223162</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223162</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223162</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205683</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205683</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205683</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223162</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223162</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42609</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34950</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52690</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>32786</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25499</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41418</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>25072</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42272</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,1%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42609</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>33895</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51482</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64165</t>
+          <t>62795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89045</t>
+          <t>88550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>123358</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>113277</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131017</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>74,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>122590</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113958</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129877</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>113104</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>130304</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,9%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>123358</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>114485</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>132072</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>74,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>232298</t>
+          <t>232793</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257178</t>
+          <t>258548</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165967</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165967</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165967</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165967</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165967</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165967</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43114</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34982</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54506</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>51209</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>40804</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>61186</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>40933</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>62563</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,44%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43114</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34045</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53199</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79729</t>
+          <t>81323</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108893</t>
+          <t>109552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>165282</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>153890</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>173414</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>158328</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>148351</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>168733</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>146974</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>168604</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>75,56%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>165282</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>155197</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>174351</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>79,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>309040</t>
+          <t>308381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>338204</t>
+          <t>336610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209537</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209537</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>151559</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>189799</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>25,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>163145</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>145285</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>183629</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>143342</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>180478</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>22,98%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>170581</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>151532</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>188742</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>307721</t>
+          <t>307512</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>361743</t>
+          <t>360492</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>580628</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>561410</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>599650</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>77,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>546808</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>526324</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>564668</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>529475</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>566611</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>77,02%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>74,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>79,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>580628</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>562467</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>599677</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1099419</t>
+          <t>1100670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1153441</t>
+          <t>1153650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>751209</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>751209</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>751209</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>709953</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>709953</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>709953</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>751209</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>751209</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>751209</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2016 (tasa de respuesta: 99,62%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30745</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23633</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40167</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>23928</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17198</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32346</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16940</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31844</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>30745</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22271</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>39986</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43761</t>
+          <t>44207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67242</t>
+          <t>67400</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>117331</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>107909</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>124443</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>109174</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>100756</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>115904</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101258</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>116162</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>82,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>117331</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>108090</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>125805</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>79,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>213936</t>
+          <t>213778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237417</t>
+          <t>236971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,28%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133102</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133102</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133102</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47923</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>38931</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>58791</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>52244</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>42718</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>62252</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>42266</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61999</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>47923</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>39432</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>58469</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86856</t>
+          <t>86578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113733</t>
+          <t>113950</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>175702</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>164834</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>184694</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>73,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>154307</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>144299</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>163833</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>144552</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>164285</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>74,71%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>79,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>175702</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>165156</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>184193</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>78,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316443</t>
+          <t>316226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>343320</t>
+          <t>343598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223625</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223625</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223625</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206551</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206551</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206551</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223625</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223625</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30391</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23333</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39122</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>30574</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23207</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38476</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>23167</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>38460</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>30391</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>22496</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>38755</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50191</t>
+          <t>51702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71687</t>
+          <t>73311</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>135110</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>126379</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>142168</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,36%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>125423</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>117521</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>132790</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>117537</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>132830</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>80,4%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>135110</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>126746</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>143005</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>81,64%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249811</t>
+          <t>248187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271307</t>
+          <t>269796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165501</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165501</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165501</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165501</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165501</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165501</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37060</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28343</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47995</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>37141</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28709</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>47320</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28109</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>46417</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>37060</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>28429</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>47045</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,2%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61592</t>
+          <t>62418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89140</t>
+          <t>87315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>166595</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>155660</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>175312</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,43%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>170279</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>160100</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>178711</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>161003</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>179311</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,09%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>166595</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>156610</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>175226</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,8%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321935</t>
+          <t>323760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>349483</t>
+          <t>348657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203655</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203655</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203655</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203655</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203655</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>127328</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>163833</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>143886</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>127645</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>161928</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>126750</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>161597</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,47%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>146119</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>129843</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>164378</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>266751</t>
+          <t>266309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>316631</t>
+          <t>314781</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>594738</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>577024</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>613529</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>836</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>559184</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>541142</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>575425</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>541473</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>576320</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,97%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>594738</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>576479</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>611014</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,28%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1127296</t>
+          <t>1129146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1177176</t>
+          <t>1177618</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -6220,52 +6220,52 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>740857</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740857</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740857</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>703070</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703070</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703070</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740857</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740857</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740857</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13098</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27592</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,92%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,4%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11646</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23499</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31408</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29566</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49343</t>
+          <t>48257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>105863</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>98314</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>112808</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,08%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>100226</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>93781</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>105634</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>85,46%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>118746</t>
+          <t>103927</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109004</t>
+          <t>96105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126036</t>
+          <t>109586</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>218973</t>
+          <t>209790</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208350</t>
+          <t>198720</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228127</t>
+          <t>218819</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,6%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36346</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56686</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21576</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>38615</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>19678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61545</t>
+          <t>35589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65442</t>
+          <t>60801</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93257</t>
+          <t>87705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>191813</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>180520</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>200860</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>161537</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>151897</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>168936</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>205299</t>
+          <t>157464</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193490</t>
+          <t>148824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216542</t>
+          <t>164735</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>366837</t>
+          <t>349277</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>352291</t>
+          <t>333914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>380106</t>
+          <t>360818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22551</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41590</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15194</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38079</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42353</t>
+          <t>32034</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74836</t>
+          <t>65902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>138158</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>126751</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145790</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>163349</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151506</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>174391</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>86,16%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>153606</t>
+          <t>132486</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142933</t>
+          <t>124170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163237</t>
+          <t>139412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>316954</t>
+          <t>270644</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>300035</t>
+          <t>258643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>332304</t>
+          <t>282096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19714</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34636</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21039</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36591</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27702</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>20664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38161</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45453</t>
+          <t>42996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68547</t>
+          <t>64836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>143273</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>134740</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>149662</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>139913</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>131371</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>146923</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>152728</t>
+          <t>139443</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143077</t>
+          <t>130541</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160320</t>
+          <t>146481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>292642</t>
+          <t>282717</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280654</t>
+          <t>271685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303748</t>
+          <t>293525</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>105312</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>138293</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>82080</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>116826</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113296</t>
+          <t>81764</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151520</t>
+          <t>111378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207822</t>
+          <t>195795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>258123</t>
+          <t>241364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>565026</t>
+          <t>579107</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>548514</t>
+          <t>562536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>583260</t>
+          <t>595517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>630380</t>
+          <t>533321</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>610452</t>
+          <t>517455</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>648676</t>
+          <t>547069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1195406</t>
+          <t>1112428</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1169189</t>
+          <t>1088298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1219490</t>
+          <t>1133867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
